--- a/02-Knowledge/investment-research/credit-card-management/信用卡主控表.xlsx
+++ b/02-Knowledge/investment-research/credit-card-management/信用卡主控表.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11565" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11565" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1-卡片信息" sheetId="1" state="visible" r:id="rId1"/>
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="宋体"/>
       <family val="2"/>
@@ -117,9 +117,17 @@
     </font>
     <font>
       <name val="微软雅黑"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <charset val="134"/>
+      <family val="2"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <family val="2"/>
+      <i val="1"/>
+      <color rgb="FF808080"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="微软雅黑"/>
@@ -127,12 +135,11 @@
     </font>
     <font>
       <name val="微软雅黑"/>
-      <i val="1"/>
-      <color rgb="00808080"/>
-      <sz val="9"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -177,32 +184,38 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor rgb="FFFFCC99"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFCC99"/>
-        <bgColor rgb="00FFCC99"/>
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -272,7 +285,9 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -311,7 +326,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -334,10 +349,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -350,29 +361,12 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="58" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -381,35 +375,13 @@
     <xf numFmtId="57" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -421,11 +393,53 @@
     <xf numFmtId="0" fontId="10" fillId="9" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="12">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -463,70 +477,6 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -952,21 +902,21 @@
   <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
-    <col width="5" customWidth="1" style="17" min="1" max="1"/>
-    <col width="8" customWidth="1" style="17" min="2" max="2"/>
-    <col width="12" customWidth="1" style="17" min="3" max="3"/>
-    <col width="10" customWidth="1" style="17" min="4" max="6"/>
-    <col width="7" customWidth="1" style="17" min="7" max="7"/>
+    <col width="5" customWidth="1" style="25" min="1" max="1"/>
+    <col width="8" customWidth="1" style="25" min="2" max="2"/>
+    <col width="12" customWidth="1" style="25" min="3" max="3"/>
+    <col width="10" customWidth="1" style="25" min="4" max="6"/>
+    <col width="7" customWidth="1" style="25" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" s="17">
-      <c r="A1" s="18" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="25">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>信用卡卡片总览 — 韩伟</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="24.95" customHeight="1" s="17">
+    <row r="2" ht="24.95" customHeight="1" s="25">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>序号</t>
@@ -1003,21 +953,21 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="16.5" customHeight="1" s="17">
-      <c r="A3" s="10" t="n">
+    <row r="3" ht="16.5" customHeight="1" s="25">
+      <c r="A3" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>兴业</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>行悠白</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1028,27 +978,27 @@
       <c r="F3" s="2" t="n">
         <v>78000</v>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>5日</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1" s="17">
-      <c r="A4" s="10" t="n">
+    <row r="4" ht="16.5" customHeight="1" s="25">
+      <c r="A4" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>平安</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>精英白</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1059,27 +1009,27 @@
       <c r="F4" s="2" t="n">
         <v>45000</v>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>7日</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="16.5" customHeight="1" s="17">
-      <c r="A5" s="10" t="n">
+    <row r="5" ht="16.5" customHeight="1" s="25">
+      <c r="A5" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>宁波</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>菁英卡</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1090,27 +1040,27 @@
       <c r="F5" s="2" t="n">
         <v>100000</v>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>8日</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="16.5" customHeight="1" s="17">
-      <c r="A6" s="10" t="n">
+    <row r="6" ht="16.5" customHeight="1" s="25">
+      <c r="A6" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>农行</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>精粹白</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1121,27 +1071,27 @@
       <c r="F6" s="2" t="n">
         <v>90000</v>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>10日</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1" s="17">
-      <c r="A7" s="10" t="n">
+    <row r="7" ht="16.5" customHeight="1" s="25">
+      <c r="A7" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>交通</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>东航航空卡</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1152,27 +1102,27 @@
       <c r="F7" s="2" t="n">
         <v>59000</v>
       </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>13日</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="16.5" customHeight="1" s="17">
-      <c r="A8" s="10" t="n">
+    <row r="8" ht="16.5" customHeight="1" s="25">
+      <c r="A8" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>招商</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>飞鸟白</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1183,27 +1133,27 @@
       <c r="F8" s="2" t="n">
         <v>102000</v>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>15日</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1" s="17">
-      <c r="A9" s="10" t="n">
+    <row r="9" ht="16.5" customHeight="1" s="25">
+      <c r="A9" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>中信</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>南航航空卡</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1214,27 +1164,27 @@
       <c r="F9" s="2" t="n">
         <v>80000</v>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>17日</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1" s="17">
-      <c r="A10" s="10" t="n">
+    <row r="10" ht="16.5" customHeight="1" s="25">
+      <c r="A10" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>民生</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>百夫长</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1245,27 +1195,27 @@
       <c r="F10" s="2" t="n">
         <v>60000</v>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>19日</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1" s="17">
-      <c r="A11" s="10" t="n">
+    <row r="11" ht="16.5" customHeight="1" s="25">
+      <c r="A11" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>邮储</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>鼎致白</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1276,27 +1226,27 @@
       <c r="F11" s="2" t="n">
         <v>75000</v>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>20日</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1" s="17">
-      <c r="A12" s="10" t="n">
+    <row r="12" ht="16.5" customHeight="1" s="25">
+      <c r="A12" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>浦发</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>南航航空卡</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1307,27 +1257,27 @@
       <c r="F12" s="2" t="n">
         <v>50000</v>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>22日</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1" s="17">
-      <c r="A13" s="10" t="n">
+    <row r="13" ht="16.5" customHeight="1" s="25">
+      <c r="A13" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>中国银行</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1338,27 +1288,27 @@
       <c r="F13" s="2" t="n">
         <v>26000</v>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>22日</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1" s="17">
-      <c r="A14" s="10" t="n">
+    <row r="14" ht="16.5" customHeight="1" s="25">
+      <c r="A14" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>建行</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>大山白</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1369,27 +1319,27 @@
       <c r="F14" s="2" t="n">
         <v>95000</v>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>23日</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1" s="17">
-      <c r="A15" s="10" t="n">
+    <row r="15" ht="16.5" customHeight="1" s="25">
+      <c r="A15" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>广发</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>尊旅卡</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1400,27 +1350,27 @@
       <c r="F15" s="2" t="n">
         <v>71500</v>
       </c>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>25日</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="16.5" customHeight="1" s="17">
-      <c r="A16" s="10" t="n">
+    <row r="16" ht="16.5" customHeight="1" s="25">
+      <c r="A16" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>光大</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>阳光车主</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1431,27 +1381,27 @@
       <c r="F16" s="2" t="n">
         <v>50000</v>
       </c>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>25日</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="16.5" customHeight="1" s="17">
-      <c r="A17" s="10" t="n">
+    <row r="17" ht="16.5" customHeight="1" s="25">
+      <c r="A17" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>工商</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>大白</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1462,27 +1412,27 @@
       <c r="F17" s="2" t="n">
         <v>100000</v>
       </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>26日</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="16.5" customHeight="1" s="17">
-      <c r="A18" s="10" t="n">
+    <row r="18" ht="16.5" customHeight="1" s="25">
+      <c r="A18" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>京彩卡</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1493,32 +1443,31 @@
       <c r="F18" s="2" t="n">
         <v>60000</v>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>27日</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="16.5" customHeight="1" s="17">
-      <c r="A19" s="29" t="inlineStr">
+    <row r="19" ht="16.5" customHeight="1" s="25">
+      <c r="A19" s="35" t="inlineStr">
         <is>
           <t>合计（16张）</t>
         </is>
       </c>
-      <c r="B19" s="14" t="n"/>
-      <c r="C19" s="14" t="n"/>
-      <c r="D19" s="15" t="n"/>
+      <c r="B19" s="28" t="n"/>
+      <c r="C19" s="28" t="n"/>
+      <c r="D19" s="29" t="n"/>
       <c r="E19" s="3" t="n">
         <v>919000</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>1141500</v>
       </c>
-      <c r="G19" s="13" t="n"/>
-    </row>
-    <row r="20"/>
-    <row r="21" ht="15.75" customHeight="1" s="17">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="G19" s="11" t="n"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1" s="25">
+      <c r="A21" s="24" t="inlineStr">
         <is>
           <t>条件格式：✅=绿色(已达标) | ⚠️=黄色(进行中) | ❌=红色(未完成) | 待补充：卡号后4位、爱人卡片</t>
         </is>
@@ -1543,44 +1492,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
-    <col width="10" customWidth="1" style="17" min="1" max="1"/>
-    <col width="12" customWidth="1" style="17" min="2" max="2"/>
-    <col width="14" customWidth="1" style="17" min="3" max="3"/>
-    <col width="12" customWidth="1" style="17" min="4" max="4"/>
-    <col width="8" customWidth="1" style="17" min="5" max="5"/>
-    <col width="18" customWidth="1" style="17" min="6" max="6"/>
-    <col width="13.875" customWidth="1" style="17" min="7" max="7"/>
-    <col width="8" customWidth="1" style="17" min="8" max="8"/>
-    <col width="24.125" customWidth="1" style="26" min="9" max="9"/>
+    <col width="10" customWidth="1" style="25" min="1" max="1"/>
+    <col width="12" customWidth="1" style="25" min="2" max="2"/>
+    <col width="14" customWidth="1" style="25" min="3" max="3"/>
+    <col width="12" customWidth="1" style="25" min="4" max="4"/>
+    <col width="8" customWidth="1" style="25" min="5" max="5"/>
+    <col width="18" customWidth="1" style="25" min="6" max="6"/>
+    <col width="13.875" customWidth="1" style="25" min="7" max="7"/>
+    <col width="8" customWidth="1" style="25" min="8" max="8"/>
+    <col width="25.875" customWidth="1" style="25" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" s="17">
-      <c r="A1" s="18" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="25">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>年费追踪 — 按4种类型分组</t>
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3" ht="15" customHeight="1" s="17">
-      <c r="A3" s="30" t="inlineStr">
+    <row r="3" ht="15" customHeight="1" s="25">
+      <c r="A3" s="36" t="inlineStr">
         <is>
           <t>A. 积分抵扣类</t>
         </is>
       </c>
-      <c r="B3" s="14" t="n"/>
-      <c r="C3" s="14" t="n"/>
-      <c r="D3" s="14" t="n"/>
-      <c r="E3" s="14" t="n"/>
-      <c r="F3" s="14" t="n"/>
-      <c r="G3" s="14" t="n"/>
-      <c r="H3" s="14" t="n"/>
-      <c r="J3" s="15" t="n"/>
-    </row>
-    <row r="4" ht="33" customHeight="1" s="17">
+      <c r="B3" s="28" t="n"/>
+      <c r="C3" s="28" t="n"/>
+      <c r="D3" s="28" t="n"/>
+      <c r="E3" s="28" t="n"/>
+      <c r="F3" s="28" t="n"/>
+      <c r="G3" s="28" t="n"/>
+      <c r="H3" s="29" t="n"/>
+      <c r="I3" s="29" t="n"/>
+    </row>
+    <row r="4" ht="33" customHeight="1" s="25">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>银行</t>
@@ -1621,245 +1569,220 @@
           <t>2026状态</t>
         </is>
       </c>
-      <c r="I4" s="31" t="inlineStr">
-        <is>
-          <t>到期提醒</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="16.5" customHeight="1" s="17">
-      <c r="A5" s="10" t="inlineStr">
+    <row r="5" ht="16.5" customHeight="1" s="25">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>建行</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>大山白</t>
         </is>
       </c>
-      <c r="C5" s="10" t="n">
+      <c r="C5" s="8" t="n">
         <v>400000</v>
       </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>龙支付3倍\支付宝2倍</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>年底</t>
         </is>
       </c>
-      <c r="H5" s="32" t="inlineStr">
+      <c r="H5" s="18" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="I5" s="33" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="J5" s="25" t="inlineStr">
+      <c r="I5" s="15" t="inlineStr">
         <is>
           <t>银行APP直接搜索年费查询</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="16.5" customHeight="1" s="17">
-      <c r="A6" s="10" t="inlineStr">
+    <row r="6" ht="16.5" customHeight="1" s="25">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>邮储</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>鼎致白</t>
         </is>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="8" t="n">
         <v>200000</v>
       </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>生日双倍</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>2月</t>
         </is>
       </c>
-      <c r="H6" s="32" t="inlineStr">
+      <c r="H6" s="18" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="I6" s="33" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="J6" s="25" t="inlineStr">
+      <c r="I6" s="15" t="inlineStr">
         <is>
           <t>银行APP直接搜索年费查询</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1" s="17">
-      <c r="A7" s="10" t="inlineStr">
+    <row r="7" ht="16.5" customHeight="1" s="25">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>光大</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>阳光车主</t>
         </is>
       </c>
-      <c r="C7" s="10" t="n">
+      <c r="C7" s="8" t="n">
         <v>100000</v>
       </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>微信5/10倍活动</t>
         </is>
       </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" s="34" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" s="19" t="inlineStr">
         <is>
           <t>⚠️</t>
         </is>
       </c>
-      <c r="I7" s="35" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="J7" s="25" t="inlineStr">
+      <c r="I7" s="15" t="inlineStr">
         <is>
           <t>银行APP直接搜索年费查询</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="26.25" customHeight="1" s="17">
-      <c r="A8" s="10" t="inlineStr">
+    <row r="8" ht="26.25" customHeight="1" s="25">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>民生</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>百夫长</t>
         </is>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="8" t="n">
         <v>200000</v>
       </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>支付宝</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>4月</t>
         </is>
       </c>
-      <c r="H8" s="32" t="inlineStr">
+      <c r="H8" s="18" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="I8" s="33" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="J8" s="27" t="inlineStr">
+      <c r="I8" s="16" t="inlineStr">
         <is>
           <t>26年是打客服电话问的
 积分够自动抵扣</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1" s="17">
-      <c r="A9" s="10" t="n"/>
-      <c r="B9" s="10" t="n"/>
-      <c r="C9" s="10" t="n"/>
-      <c r="D9" s="10" t="n"/>
-      <c r="E9" s="10" t="n"/>
-      <c r="F9" s="10" t="n"/>
-      <c r="G9" s="10" t="n"/>
-      <c r="H9" s="10" t="n"/>
-      <c r="J9" s="25" t="n"/>
-    </row>
-    <row r="10" ht="16.5" customHeight="1" s="17">
-      <c r="A10" s="30" t="inlineStr">
+    <row r="9" ht="16.5" customHeight="1" s="25">
+      <c r="A9" s="8" t="n"/>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="8" t="n"/>
+      <c r="H9" s="8" t="n"/>
+      <c r="I9" s="15" t="n"/>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" s="25">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>B. 刷卡笔数类</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n"/>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="14" t="n"/>
-      <c r="E10" s="14" t="n"/>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="14" t="n"/>
-      <c r="H10" s="14" t="n"/>
-      <c r="J10" s="15" t="n"/>
-    </row>
-    <row r="11" ht="16.5" customHeight="1" s="17">
+      <c r="B10" s="28" t="n"/>
+      <c r="C10" s="28" t="n"/>
+      <c r="D10" s="28" t="n"/>
+      <c r="E10" s="28" t="n"/>
+      <c r="F10" s="28" t="n"/>
+      <c r="G10" s="28" t="n"/>
+      <c r="H10" s="29" t="n"/>
+      <c r="I10" s="29" t="n"/>
+    </row>
+    <row r="11" ht="16.5" customHeight="1" s="25">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>银行</t>
@@ -1900,298 +1823,273 @@
           <t>2026状态</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="31.5" customHeight="1" s="17">
-      <c r="A12" s="10" t="inlineStr">
+    <row r="12" ht="31.5" customHeight="1" s="25">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>农行</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>精粹白</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>30笔</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="n">
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="21" t="n">
+      <c r="F12" s="14" t="n">
         <v>46106</v>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>APP购买微信多倍积分</t>
         </is>
       </c>
-      <c r="H12" s="32" t="inlineStr">
+      <c r="H12" s="18" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="I12" s="33" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="J12" s="25" t="inlineStr">
+      <c r="I12" s="15" t="inlineStr">
         <is>
           <t>银行APP-信用卡-全部功能-年费查询</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1" s="17">
-      <c r="A13" s="10" t="inlineStr">
+    <row r="13" ht="16.5" customHeight="1" s="25">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>广发</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>尊旅卡</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>48笔</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="n">
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="21" t="n">
+      <c r="F13" s="14" t="n">
         <v>46234</v>
       </c>
-      <c r="G13" s="10" t="n"/>
-      <c r="H13" s="32" t="inlineStr">
+      <c r="G13" s="8" t="n"/>
+      <c r="H13" s="18" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="I13" s="33" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="J13" s="25" t="inlineStr">
+      <c r="I13" s="15" t="inlineStr">
         <is>
           <t>银行APP直接搜索年费查询</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1" s="17">
-      <c r="A14" s="10" t="inlineStr">
+    <row r="14" ht="16.5" customHeight="1" s="25">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>中国银行</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>12笔+5000元</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="n">
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="21" t="n">
+      <c r="F14" s="14" t="n">
         <v>46317</v>
       </c>
-      <c r="G14" s="10" t="n"/>
-      <c r="H14" s="32" t="inlineStr">
+      <c r="G14" s="8" t="n"/>
+      <c r="H14" s="18" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="I14" s="33" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="J14" s="25" t="inlineStr">
+      <c r="I14" s="15" t="inlineStr">
         <is>
           <t>银行APP直接搜索年费查询</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30.75" customHeight="1" s="17">
-      <c r="A15" s="10" t="inlineStr">
+    <row r="15" ht="30.75" customHeight="1" s="25">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>京彩卡</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>5笔</t>
         </is>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D15" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E15" s="10" t="n">
+      <c r="E15" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="21" t="n">
+      <c r="F15" s="14" t="n">
         <v>46080</v>
       </c>
-      <c r="G15" s="10" t="n"/>
-      <c r="H15" s="32" t="inlineStr">
+      <c r="G15" s="8" t="n"/>
+      <c r="H15" s="18" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="I15" s="33" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="J15" s="25" t="inlineStr">
+      <c r="I15" s="15" t="inlineStr">
         <is>
           <t>掌上精彩-我的-银行卡-年费</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="16.5" customHeight="1" s="17">
-      <c r="A16" s="10" t="inlineStr">
+    <row r="16" ht="16.5" customHeight="1" s="25">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>工商</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>大白</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>15笔|10000元</t>
         </is>
       </c>
-      <c r="D16" s="10" t="n">
+      <c r="D16" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="E16" s="10" t="n">
+      <c r="E16" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="n"/>
-      <c r="H16" s="32" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="18" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="I16" s="33" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="J16" s="25" t="inlineStr">
+      <c r="I16" s="15" t="inlineStr">
         <is>
           <t>工银e生活-搜索年费</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="16.5" customHeight="1" s="17">
-      <c r="A17" s="10" t="inlineStr">
+    <row r="17" ht="16.5" customHeight="1" s="25">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>浦发</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>南航卡</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>6笔</t>
         </is>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D17" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="E17" s="10" t="n">
+      <c r="E17" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F17" s="21" t="n">
+      <c r="F17" s="14" t="n">
         <v>46044</v>
       </c>
-      <c r="G17" s="10" t="n"/>
-      <c r="H17" s="32" t="inlineStr">
+      <c r="G17" s="8" t="n"/>
+      <c r="H17" s="18" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="J17" s="25" t="inlineStr">
+      <c r="I17" s="15" t="inlineStr">
         <is>
           <t>浦大喜奔-搜索年费</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="16.5" customHeight="1" s="17">
-      <c r="A18" s="10" t="n"/>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="10" t="n"/>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="10" t="n"/>
-      <c r="H18" s="10" t="n"/>
-      <c r="J18" s="25" t="n"/>
-    </row>
-    <row r="19" ht="16.5" customHeight="1" s="17">
-      <c r="A19" s="30" t="inlineStr">
+    <row r="18" ht="16.5" customHeight="1" s="25">
+      <c r="A18" s="8" t="n"/>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="8" t="n"/>
+      <c r="H18" s="8" t="n"/>
+      <c r="I18" s="15" t="n"/>
+    </row>
+    <row r="19" ht="16.5" customHeight="1" s="25">
+      <c r="A19" s="36" t="inlineStr">
         <is>
           <t>C. 消费额度类</t>
         </is>
       </c>
-      <c r="B19" s="14" t="n"/>
-      <c r="C19" s="14" t="n"/>
-      <c r="D19" s="14" t="n"/>
-      <c r="E19" s="14" t="n"/>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="14" t="n"/>
-      <c r="H19" s="14" t="n"/>
-      <c r="J19" s="15" t="n"/>
-    </row>
-    <row r="20" ht="16.5" customHeight="1" s="17">
+      <c r="B19" s="28" t="n"/>
+      <c r="C19" s="28" t="n"/>
+      <c r="D19" s="28" t="n"/>
+      <c r="E19" s="28" t="n"/>
+      <c r="F19" s="28" t="n"/>
+      <c r="G19" s="28" t="n"/>
+      <c r="H19" s="29" t="n"/>
+      <c r="I19" s="29" t="n"/>
+    </row>
+    <row r="20" ht="16.5" customHeight="1" s="25">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>银行</t>
@@ -2232,178 +2130,162 @@
           <t>2026状态</t>
         </is>
       </c>
-      <c r="I20" s="36" t="n"/>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="16.5" customHeight="1" s="17">
-      <c r="A21" s="10" t="inlineStr">
+    <row r="21" ht="16.5" customHeight="1" s="25">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>招商</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>飞鸟白</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>8W</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>8W</t>
         </is>
       </c>
-      <c r="E21" s="10" t="n">
+      <c r="E21" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F21" s="21" t="n">
+      <c r="F21" s="14" t="n">
         <v>46233</v>
       </c>
-      <c r="G21" s="10" t="n"/>
-      <c r="H21" s="32" t="inlineStr">
+      <c r="G21" s="8" t="n"/>
+      <c r="H21" s="18" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="I21" s="33" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="J21" s="27" t="inlineStr">
+      <c r="I21" s="16" t="inlineStr">
         <is>
           <t>26年是打客服电话问的</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="16.5" customHeight="1" s="17">
-      <c r="A22" s="10" t="inlineStr">
+    <row r="22" ht="16.5" customHeight="1" s="25">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>平安</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>精英白</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>12W</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>12W</t>
         </is>
       </c>
-      <c r="E22" s="10" t="n">
+      <c r="E22" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>8月</t>
         </is>
       </c>
-      <c r="G22" s="10" t="n"/>
-      <c r="H22" s="32" t="inlineStr">
+      <c r="G22" s="8" t="n"/>
+      <c r="H22" s="18" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="I22" s="33" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="J22" s="25" t="inlineStr">
+      <c r="I22" s="15" t="inlineStr">
         <is>
           <t>银行APP直接搜索年费查询</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="30.75" customHeight="1" s="17">
-      <c r="A23" s="10" t="inlineStr">
+    <row r="23" ht="30.75" customHeight="1" s="25">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>宁波</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>菁英卡</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>18W</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E23" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="10" t="n"/>
-      <c r="H23" s="34" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="n"/>
+      <c r="H23" s="19" t="inlineStr">
         <is>
           <t>⚠️</t>
         </is>
       </c>
-      <c r="I23" s="35" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="J23" s="27" t="inlineStr">
+      <c r="I23" s="16" t="inlineStr">
         <is>
           <t>26年是刚性收取1800，后续可以APP搜索年费查询</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="16.5" customHeight="1" s="17">
-      <c r="A24" s="10" t="n"/>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
-      <c r="E24" s="10" t="n"/>
-      <c r="F24" s="10" t="n"/>
-      <c r="G24" s="10" t="n"/>
-      <c r="H24" s="10" t="n"/>
-      <c r="J24" s="25" t="n"/>
-    </row>
-    <row r="25" ht="16.5" customHeight="1" s="17">
-      <c r="A25" s="30" t="inlineStr">
+    <row r="24" ht="16.5" customHeight="1" s="25">
+      <c r="A24" s="8" t="n"/>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="8" t="n"/>
+      <c r="H24" s="8" t="n"/>
+      <c r="I24" s="15" t="n"/>
+    </row>
+    <row r="25" ht="16.5" customHeight="1" s="25">
+      <c r="A25" s="36" t="inlineStr">
         <is>
           <t>D. 刚性年费类</t>
         </is>
       </c>
-      <c r="B25" s="14" t="n"/>
-      <c r="C25" s="14" t="n"/>
-      <c r="D25" s="14" t="n"/>
-      <c r="E25" s="14" t="n"/>
-      <c r="F25" s="14" t="n"/>
-      <c r="G25" s="14" t="n"/>
-      <c r="H25" s="14" t="n"/>
-      <c r="J25" s="15" t="n"/>
-    </row>
-    <row r="26" ht="16.5" customHeight="1" s="17">
+      <c r="B25" s="28" t="n"/>
+      <c r="C25" s="28" t="n"/>
+      <c r="D25" s="28" t="n"/>
+      <c r="E25" s="28" t="n"/>
+      <c r="F25" s="28" t="n"/>
+      <c r="G25" s="28" t="n"/>
+      <c r="H25" s="29" t="n"/>
+      <c r="I25" s="29" t="n"/>
+    </row>
+    <row r="26" ht="16.5" customHeight="1" s="25">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>银行</t>
@@ -2444,148 +2326,137 @@
           <t>2026状态</t>
         </is>
       </c>
-      <c r="J26" s="4" t="inlineStr">
+      <c r="I26" s="4" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="16.5" customHeight="1" s="17">
-      <c r="A27" s="10" t="inlineStr">
+    <row r="27" ht="16.5" customHeight="1" s="25">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>中信</t>
         </is>
       </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>南航卡</t>
         </is>
       </c>
-      <c r="C27" s="10" t="n">
+      <c r="C27" s="8" t="n">
         <v>480</v>
       </c>
-      <c r="D27" s="10" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>4月24日</t>
         </is>
       </c>
-      <c r="E27" s="10" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t>南航里程</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F27" s="8" t="inlineStr">
         <is>
           <t>保留</t>
         </is>
       </c>
-      <c r="G27" s="10" t="n"/>
-      <c r="H27" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I27" s="33" t="inlineStr">
-        <is>
-          <t>已过</t>
-        </is>
-      </c>
-      <c r="J27" s="25" t="n"/>
-    </row>
-    <row r="28" ht="33" customHeight="1" s="17">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="G27" s="8" t="n"/>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I27" s="15" t="n"/>
+    </row>
+    <row r="28" ht="33" customHeight="1" s="25">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>交通</t>
         </is>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>东航卡</t>
         </is>
       </c>
-      <c r="C28" s="10" t="n">
+      <c r="C28" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>12月30日</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>东航里程+代驾</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr">
+      <c r="F28" s="8" t="inlineStr">
         <is>
           <t>保留</t>
         </is>
       </c>
-      <c r="G28" s="10" t="n"/>
-      <c r="H28" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I28" s="33" t="inlineStr">
-        <is>
-          <t>已过</t>
-        </is>
-      </c>
-      <c r="J28" s="25" t="inlineStr">
+      <c r="G28" s="8" t="n"/>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I28" s="15" t="inlineStr">
         <is>
           <t>沃德用户年费减半是500</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="33" customHeight="1" s="17">
-      <c r="A29" s="10" t="inlineStr">
+    <row r="29" ht="33" customHeight="1" s="25">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>兴业</t>
         </is>
       </c>
-      <c r="B29" s="10" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>行悠白</t>
         </is>
       </c>
-      <c r="C29" s="10" t="n">
+      <c r="C29" s="8" t="n">
         <v>900</v>
       </c>
-      <c r="D29" s="10" t="inlineStr">
+      <c r="D29" s="8" t="inlineStr">
         <is>
           <t>8月26日</t>
         </is>
       </c>
-      <c r="E29" s="10" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
         <is>
           <t>接送机+贵宾厅</t>
         </is>
       </c>
-      <c r="F29" s="34" t="inlineStr">
+      <c r="F29" s="19" t="inlineStr">
         <is>
           <t>待评估</t>
         </is>
       </c>
-      <c r="G29" s="10" t="n"/>
-      <c r="H29" s="10" t="inlineStr">
-        <is>
-          <t>12378投诉</t>
-        </is>
-      </c>
-      <c r="I29" s="37" t="inlineStr">
-        <is>
-          <t>⚠️8月到期</t>
-        </is>
-      </c>
-      <c r="J29" s="27" t="inlineStr">
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>12378投诉 申请减免年费</t>
+        </is>
+      </c>
+      <c r="H29" s="34" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="I29" s="16" t="inlineStr">
         <is>
           <t>计划26年7月申请注销</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="38" t="inlineStr">
+    <row r="32" ht="15.75" customHeight="1" s="25">
+      <c r="A32" s="31" t="inlineStr">
         <is>
           <t>到期提醒说明：橙色=即将到期（1个月内）| 黄色=未到但需关注 | 绿色=已完成/已过</t>
         </is>
@@ -2593,14 +2464,14 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A25:I25"/>
-    <mergeCell ref="A19:I19"/>
-    <mergeCell ref="A10:I10"/>
-    <mergeCell ref="A32:I32"/>
-    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A19:H19"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A32:H32"/>
   </mergeCells>
-  <conditionalFormatting sqref="H4:H9 H11:H13 H15:H16 H18 H20:H24 H26:H29">
+  <conditionalFormatting sqref="H4:H9 H11:H13 H15:H16 H18 H20:H24 H26:H28">
     <cfRule type="cellIs" priority="15" operator="equal" dxfId="2">
       <formula>"✅"</formula>
     </cfRule>
@@ -2613,38 +2484,6 @@
       <formula>"✅"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="4" operator="equal" dxfId="0">
-      <formula>"⚠️"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I4">
-    <cfRule type="cellIs" priority="11" operator="equal" dxfId="2">
-      <formula>"✅"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="12" operator="equal" dxfId="0">
-      <formula>"⚠️"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I11">
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="2">
-      <formula>"✅"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" dxfId="0">
-      <formula>"⚠️"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I20">
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="2">
-      <formula>"✅"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="0">
-      <formula>"⚠️"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I26">
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="2">
-      <formula>"✅"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
       <formula>"⚠️"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2670,29 +2509,28 @@
   <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
-    <col width="8" customWidth="1" style="17" min="1" max="1"/>
-    <col width="10" customWidth="1" style="17" min="2" max="2"/>
-    <col width="14" customWidth="1" style="17" min="3" max="3"/>
-    <col width="10" customWidth="1" style="17" min="4" max="4"/>
-    <col width="10" customWidth="1" style="17" min="5" max="5"/>
-    <col width="18" customWidth="1" style="17" min="6" max="6"/>
+    <col width="8" customWidth="1" style="25" min="1" max="1"/>
+    <col width="10" customWidth="1" style="25" min="2" max="2"/>
+    <col width="14" customWidth="1" style="25" min="3" max="3"/>
+    <col width="10" customWidth="1" style="25" min="4" max="5"/>
+    <col width="18" customWidth="1" style="25" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" s="17">
-      <c r="A1" s="18" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="25">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>0账单还款日历 — 账单日=还款日，当天还清</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="17">
-      <c r="A2" s="16" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="25">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>规则：账单日 = 还款日，当天还清 → 征信报告显示0账单 | 操作：手机日历设提醒 → 当天云闪付还款 → Excel打✅</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="17">
+    <row r="3" ht="15" customHeight="1" s="25">
       <c r="A3" s="1" t="inlineStr">
         <is>
           <t>账单日</t>
@@ -2708,7 +2546,7 @@
           <t>卡种</t>
         </is>
       </c>
-      <c r="D3" s="28" t="inlineStr">
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t>还款金额</t>
         </is>
@@ -2724,521 +2562,520 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1" s="17">
-      <c r="A4" s="10" t="inlineStr">
+    <row r="4" ht="16.5" customHeight="1" s="25">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>5日</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>兴业</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>行悠白</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E4" s="39" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16.5" customHeight="1" s="17">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16.5" customHeight="1" s="25">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>7日</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>平安</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>精英白</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16.5" customHeight="1" s="17">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16.5" customHeight="1" s="25">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>8日</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>宁波</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>菁英卡</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16.5" customHeight="1" s="17">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16.5" customHeight="1" s="25">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>10日</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>农行</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>精粹白</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16.5" customHeight="1" s="17">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16.5" customHeight="1" s="25">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>13日</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>交通</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>东航卡</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>25年无法修改</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1" s="17">
-      <c r="A9" s="10" t="inlineStr">
+    <row r="9" ht="16.5" customHeight="1" s="25">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>15日</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>招商</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>飞鸟白</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>实际16号</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1" s="17">
-      <c r="A10" s="10" t="inlineStr">
+    <row r="10" ht="16.5" customHeight="1" s="25">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>17日</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>中信</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>南航卡</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16.5" customHeight="1" s="17">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16.5" customHeight="1" s="25">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>19日</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>民生</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>百夫长</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16.5" customHeight="1" s="17">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16.5" customHeight="1" s="25">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>20日</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>邮储</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>鼎致白</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16.5" customHeight="1" s="17">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16.5" customHeight="1" s="25">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>22日</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>浦发</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>南航卡</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16.5" customHeight="1" s="17">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16.5" customHeight="1" s="25">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>22日</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>中国银行</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>普通白金卡</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="16.5" customHeight="1" s="17">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16.5" customHeight="1" s="25">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>23日</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>建行</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>大山白</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="16.5" customHeight="1" s="17">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16.5" customHeight="1" s="25">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>25日</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>广发</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>尊旅卡</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>25年无法修改</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="16.5" customHeight="1" s="17">
-      <c r="A17" s="10" t="inlineStr">
+    <row r="17" ht="16.5" customHeight="1" s="25">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>25日</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>光大</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>阳光车主</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16.5" customHeight="1" s="17">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16.5" customHeight="1" s="25">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>26日</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>工商</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>大白</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>实际27号</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="16.5" customHeight="1" s="17">
-      <c r="A19" s="10" t="inlineStr">
+    <row r="19" ht="16.5" customHeight="1" s="25">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>27日</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>京彩卡</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>只能选固定日期</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21" ht="15.75" customHeight="1" s="17">
-      <c r="A21" s="16" t="inlineStr">
+    <row r="21" ht="15.75" customHeight="1" s="25">
+      <c r="A21" s="24" t="inlineStr">
         <is>
           <t>注意：部分银行账单日当天还款可能T+1入账，需测试各银行。</t>
         </is>
@@ -3266,33 +3103,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
-    <col width="10" customWidth="1" style="17" min="1" max="1"/>
-    <col width="8" customWidth="1" style="17" min="2" max="2"/>
-    <col width="14" customWidth="1" style="17" min="3" max="3"/>
-    <col width="8" customWidth="1" style="17" min="4" max="4"/>
-    <col width="10" customWidth="1" style="17" min="5" max="6"/>
-    <col width="14" customWidth="1" style="17" min="7" max="8"/>
+    <col width="10" customWidth="1" style="25" min="1" max="1"/>
+    <col width="8" customWidth="1" style="25" min="2" max="2"/>
+    <col width="14" customWidth="1" style="25" min="3" max="3"/>
+    <col width="8" customWidth="1" style="25" min="4" max="4"/>
+    <col width="10" customWidth="1" style="25" min="5" max="6"/>
+    <col width="14" customWidth="1" style="25" min="7" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" s="17">
-      <c r="A1" s="18" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="25">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>权益变现 — 库存管理 + 变现流水</t>
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3" ht="15" customHeight="1" s="17">
-      <c r="A3" s="19" t="inlineStr">
+    <row r="3" ht="15" customHeight="1" s="25">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>4A. 权益库存（可卖权益汇总）</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="17">
+    <row r="4" ht="15" customHeight="1" s="25">
       <c r="A4" s="1" t="inlineStr">
         <is>
           <t>银行</t>
@@ -3334,577 +3170,615 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="16.5" customHeight="1" s="17">
-      <c r="A5" s="10" t="inlineStr">
+    <row r="5" ht="16.5" customHeight="1" s="25">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>建行</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>接送机</t>
         </is>
       </c>
-      <c r="C5" s="10" t="n">
+      <c r="C5" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="10" t="n">
+      <c r="E5" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>80-120</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>240-360</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>100km, 实名</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="33" customHeight="1" s="17">
-      <c r="A6" s="10" t="inlineStr">
+    <row r="6" ht="33" customHeight="1" s="25">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>建行</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>龙腾贵宾厅</t>
         </is>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>50-80</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>250-400</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>实名</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1" s="17">
-      <c r="A7" s="10" t="inlineStr">
+    <row r="7" ht="16.5" customHeight="1" s="25">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>邮储</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>代驾</t>
         </is>
       </c>
-      <c r="C7" s="10" t="n">
+      <c r="C7" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E7" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>50-108</t>
         </is>
       </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>300-648</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>40km, 无实名</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="16.5" customHeight="1" s="17">
-      <c r="A8" s="10" t="inlineStr">
+    <row r="8" ht="16.5" customHeight="1" s="25">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>邮储</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>接送机</t>
         </is>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E8" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>80-120</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>160-240</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>无实名</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="33" customHeight="1" s="17">
-      <c r="A9" s="10" t="inlineStr">
+    <row r="9" ht="33" customHeight="1" s="25">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>邮储</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>机场贵宾厅</t>
         </is>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E9" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>50-80</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>200-320</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>无实名</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="33" customHeight="1" s="17">
-      <c r="A10" s="10" t="inlineStr">
+    <row r="10" ht="33" customHeight="1" s="25">
+      <c r="A10" s="37" t="inlineStr">
+        <is>
+          <t>邮储</t>
+        </is>
+      </c>
+      <c r="B10" s="37" t="inlineStr">
+        <is>
+          <t>高铁贵宾厅</t>
+        </is>
+      </c>
+      <c r="C10" s="37" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="37" t="n">
+        <v>6</v>
+      </c>
+      <c r="F10" s="37" t="inlineStr">
+        <is>
+          <t>50-80</t>
+        </is>
+      </c>
+      <c r="G10" s="37" t="inlineStr">
+        <is>
+          <t>300-480</t>
+        </is>
+      </c>
+      <c r="H10" s="37" t="inlineStr">
+        <is>
+          <t>可吃饭,可带人</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16.5" customHeight="1" s="25">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>工商</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>龙腾休息室</t>
         </is>
       </c>
-      <c r="C10" s="10" t="n">
+      <c r="C11" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D11" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E11" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>50-80</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>300-480</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>实名</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1" s="17">
-      <c r="A11" s="10" t="inlineStr">
+    <row r="12" ht="33" customHeight="1" s="25">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>工商</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>接送机</t>
         </is>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C12" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D12" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="E12" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="33" customHeight="1" s="17">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="33" customHeight="1" s="25">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>兴业</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>境内接送机</t>
         </is>
       </c>
-      <c r="C12" s="10" t="n">
+      <c r="C13" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D13" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="E13" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>80-120</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>320-480</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>境内</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="33" customHeight="1" s="17">
-      <c r="A13" s="10" t="inlineStr">
+    <row r="14" ht="16.5" customHeight="1" s="25">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>兴业</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>境外接送机</t>
         </is>
       </c>
-      <c r="C13" s="10" t="n">
+      <c r="C14" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D14" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="10" t="n">
+      <c r="E14" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>200+</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>400+</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>境外</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1" s="17">
-      <c r="A14" s="10" t="inlineStr">
+    <row r="15" ht="16.5" customHeight="1" s="25">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>民生</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>休息室</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D15" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>50/次</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>100积点/次</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1" s="17">
-      <c r="A15" s="10" t="inlineStr">
+    <row r="16" ht="16.5" customHeight="1" s="25">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>宁波</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>贵宾厅</t>
         </is>
       </c>
-      <c r="C15" s="10" t="n">
+      <c r="C16" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D16" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="10" t="n">
+      <c r="E16" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>50-80</t>
         </is>
       </c>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>600-960</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>实名</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="16.5" customHeight="1" s="17">
-      <c r="A16" s="29" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="38" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="14" t="n"/>
-      <c r="E16" s="15" t="n"/>
-      <c r="F16" s="29" t="inlineStr">
-        <is>
-          <t>2,850-4,988 元</t>
-        </is>
-      </c>
-      <c r="G16" s="15" t="n"/>
-      <c r="H16" s="13" t="n"/>
-    </row>
-    <row r="17"/>
-    <row r="18" ht="15" customHeight="1" s="17">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="B17" s="39" t="n"/>
+      <c r="C17" s="39" t="n"/>
+      <c r="D17" s="39" t="n"/>
+      <c r="E17" s="39" t="n"/>
+      <c r="F17" s="38" t="inlineStr">
+        <is>
+          <t>3,150-5,468 元</t>
+        </is>
+      </c>
+      <c r="G17" s="39" t="n"/>
+      <c r="H17" s="40" t="n"/>
+    </row>
+    <row r="18" ht="15" customHeight="1" s="25"/>
+    <row r="19" ht="15" customHeight="1" s="25">
+      <c r="A19" s="32" t="inlineStr">
         <is>
           <t>4B. 变现流水</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="17">
-      <c r="A19" s="1" t="inlineStr">
+    <row r="20" ht="16.5" customHeight="1" s="25">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr">
+      <c r="B20" s="1" t="inlineStr">
         <is>
           <t>银行</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>权益</t>
         </is>
       </c>
-      <c r="D19" s="1" t="inlineStr">
+      <c r="D20" s="1" t="inlineStr">
         <is>
           <t>售价(元)</t>
         </is>
       </c>
-      <c r="E19" s="1" t="inlineStr">
+      <c r="E20" s="1" t="inlineStr">
         <is>
           <t>买家</t>
         </is>
       </c>
-      <c r="F19" s="1" t="inlineStr">
+      <c r="F20" s="1" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="G19" s="1" t="inlineStr">
+      <c r="G20" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="H19" s="1" t="n"/>
-    </row>
-    <row r="20" ht="16.5" customHeight="1" s="17">
-      <c r="A20" s="10" t="n"/>
-      <c r="B20" s="10" t="n"/>
-      <c r="C20" s="10" t="n"/>
-      <c r="D20" s="10" t="n"/>
-      <c r="E20" s="10" t="n"/>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="10" t="n"/>
-      <c r="H20" s="10" t="n"/>
-    </row>
-    <row r="21" ht="16.5" customHeight="1" s="17">
-      <c r="A21" s="10" t="n"/>
-      <c r="B21" s="10" t="n"/>
-      <c r="C21" s="10" t="n"/>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="10" t="n"/>
-      <c r="F21" s="10" t="n"/>
-      <c r="G21" s="10" t="n"/>
-      <c r="H21" s="10" t="n"/>
-    </row>
-    <row r="22" ht="16.5" customHeight="1" s="17">
-      <c r="A22" s="10" t="n"/>
-      <c r="B22" s="10" t="n"/>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="10" t="n"/>
-      <c r="E22" s="10" t="n"/>
-      <c r="F22" s="10" t="n"/>
-      <c r="G22" s="10" t="n"/>
-      <c r="H22" s="10" t="n"/>
-    </row>
-    <row r="23" ht="16.5" customHeight="1" s="17">
-      <c r="A23" s="10" t="n"/>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
-      <c r="E23" s="10" t="n"/>
-      <c r="F23" s="10" t="n"/>
-      <c r="G23" s="10" t="n"/>
-      <c r="H23" s="10" t="n"/>
-    </row>
-    <row r="24" ht="16.5" customHeight="1" s="17">
-      <c r="A24" s="10" t="n"/>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
-      <c r="E24" s="10" t="n"/>
-      <c r="F24" s="10" t="n"/>
-      <c r="G24" s="10" t="n"/>
-      <c r="H24" s="10" t="n"/>
-    </row>
-    <row r="25" ht="16.5" customHeight="1" s="17">
-      <c r="A25" s="10" t="n"/>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="10" t="n"/>
-      <c r="E25" s="10" t="n"/>
-      <c r="F25" s="10" t="n"/>
-      <c r="G25" s="10" t="n"/>
-      <c r="H25" s="10" t="n"/>
-    </row>
-    <row r="26" ht="16.5" customHeight="1" s="17">
-      <c r="A26" s="10" t="n"/>
-      <c r="B26" s="10" t="n"/>
-      <c r="C26" s="10" t="n"/>
-      <c r="D26" s="10" t="n"/>
-      <c r="E26" s="10" t="n"/>
-      <c r="F26" s="10" t="n"/>
-      <c r="G26" s="10" t="n"/>
-      <c r="H26" s="10" t="n"/>
-    </row>
-    <row r="27" ht="16.5" customHeight="1" s="17">
-      <c r="A27" s="10" t="n"/>
-      <c r="B27" s="10" t="n"/>
-      <c r="C27" s="10" t="n"/>
-      <c r="D27" s="10" t="n"/>
-      <c r="E27" s="10" t="n"/>
-      <c r="F27" s="10" t="n"/>
-      <c r="G27" s="10" t="n"/>
-      <c r="H27" s="10" t="n"/>
-    </row>
-    <row r="28" ht="16.5" customHeight="1" s="17">
-      <c r="A28" s="10" t="n"/>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="n"/>
-      <c r="D28" s="10" t="n"/>
-      <c r="E28" s="10" t="n"/>
-      <c r="F28" s="10" t="n"/>
-      <c r="G28" s="10" t="n"/>
-      <c r="H28" s="10" t="n"/>
-    </row>
-    <row r="29" ht="16.5" customHeight="1" s="17">
-      <c r="A29" s="10" t="n"/>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="10" t="n"/>
-      <c r="D29" s="10" t="n"/>
-      <c r="E29" s="10" t="n"/>
-      <c r="F29" s="10" t="n"/>
-      <c r="G29" s="10" t="n"/>
-      <c r="H29" s="10" t="n"/>
+      <c r="H20" s="1" t="n"/>
+    </row>
+    <row r="21" ht="16.5" customHeight="1" s="25">
+      <c r="A21" s="8" t="n"/>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="8" t="n"/>
+      <c r="G21" s="8" t="n"/>
+      <c r="H21" s="8" t="n"/>
+    </row>
+    <row r="22" ht="16.5" customHeight="1" s="25">
+      <c r="A22" s="8" t="n"/>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="8" t="n"/>
+      <c r="H22" s="8" t="n"/>
+    </row>
+    <row r="23" ht="16.5" customHeight="1" s="25">
+      <c r="A23" s="8" t="n"/>
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="8" t="n"/>
+      <c r="F23" s="8" t="n"/>
+      <c r="G23" s="8" t="n"/>
+      <c r="H23" s="8" t="n"/>
+    </row>
+    <row r="24" ht="16.5" customHeight="1" s="25">
+      <c r="A24" s="8" t="n"/>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="8" t="n"/>
+      <c r="H24" s="8" t="n"/>
+    </row>
+    <row r="25" ht="16.5" customHeight="1" s="25">
+      <c r="A25" s="8" t="n"/>
+      <c r="B25" s="8" t="n"/>
+      <c r="C25" s="8" t="n"/>
+      <c r="D25" s="8" t="n"/>
+      <c r="E25" s="8" t="n"/>
+      <c r="F25" s="8" t="n"/>
+      <c r="G25" s="8" t="n"/>
+      <c r="H25" s="8" t="n"/>
+    </row>
+    <row r="26" ht="16.5" customHeight="1" s="25">
+      <c r="A26" s="8" t="n"/>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="8" t="n"/>
+      <c r="H26" s="8" t="n"/>
+    </row>
+    <row r="27" ht="16.5" customHeight="1" s="25">
+      <c r="A27" s="8" t="n"/>
+      <c r="B27" s="8" t="n"/>
+      <c r="C27" s="8" t="n"/>
+      <c r="D27" s="8" t="n"/>
+      <c r="E27" s="8" t="n"/>
+      <c r="F27" s="8" t="n"/>
+      <c r="G27" s="8" t="n"/>
+      <c r="H27" s="8" t="n"/>
+    </row>
+    <row r="28" ht="16.5" customHeight="1" s="25">
+      <c r="A28" s="8" t="n"/>
+      <c r="B28" s="8" t="n"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="8" t="n"/>
+      <c r="F28" s="8" t="n"/>
+      <c r="G28" s="8" t="n"/>
+      <c r="H28" s="8" t="n"/>
+    </row>
+    <row r="29" ht="16.5" customHeight="1" s="25">
+      <c r="A29" s="8" t="n"/>
+      <c r="B29" s="8" t="n"/>
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="8" t="n"/>
+      <c r="E29" s="8" t="n"/>
+      <c r="F29" s="8" t="n"/>
+      <c r="G29" s="8" t="n"/>
+      <c r="H29" s="8" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="n"/>
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="8" t="n"/>
+      <c r="G30" s="8" t="n"/>
+      <c r="H30" s="8" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="F16:G16"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="F17:G17"/>
   </mergeCells>
   <conditionalFormatting sqref="E5:E15">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1">
@@ -3925,28 +3799,27 @@
   <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
-    <col width="10" customWidth="1" style="17" min="1" max="2"/>
-    <col width="14" customWidth="1" style="17" min="3" max="3"/>
-    <col width="8" customWidth="1" style="17" min="4" max="4"/>
-    <col width="10" customWidth="1" style="17" min="5" max="8"/>
+    <col width="10" customWidth="1" style="25" min="1" max="2"/>
+    <col width="14" customWidth="1" style="25" min="3" max="3"/>
+    <col width="8" customWidth="1" style="25" min="4" max="4"/>
+    <col width="10" customWidth="1" style="25" min="5" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" s="17">
-      <c r="A1" s="18" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="25">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>活动与券 — 固定活动日历 + 变现流水</t>
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3" ht="15" customHeight="1" s="17">
-      <c r="A3" s="19" t="inlineStr">
+    <row r="3" ht="15" customHeight="1" s="25">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>5A. 固定活动日历</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="17">
+    <row r="4" ht="15" customHeight="1" s="25">
       <c r="A4" s="1" t="inlineStr">
         <is>
           <t>时间</t>
@@ -3973,124 +3846,122 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="49.5" customHeight="1" s="17">
-      <c r="A5" s="10" t="inlineStr">
+    <row r="5" ht="49.5" customHeight="1" s="25">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>每月1号</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>光大</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>微信多倍积分报名</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>微信→光大信用卡→报名</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>日历重复</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="33" customHeight="1" s="17">
-      <c r="A6" s="10" t="inlineStr">
+    <row r="6" ht="33" customHeight="1" s="25">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>每月6号</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>农行</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>航空里程兑换</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>App→里程兑换</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>日历重复</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="33" customHeight="1" s="17">
-      <c r="A7" s="10" t="inlineStr">
+    <row r="7" ht="33" customHeight="1" s="25">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>每周三</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>招商</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>周三5折抢券</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>App→精选</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>日历重复</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="33" customHeight="1" s="17">
-      <c r="A8" s="10" t="inlineStr">
+    <row r="8" ht="33" customHeight="1" s="25">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>生日月</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>邮储/光大/广发</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>生日多倍积分</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>自动</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>日历提醒</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11" ht="15" customHeight="1" s="17">
-      <c r="A11" s="19" t="inlineStr">
+    <row r="11" ht="15" customHeight="1" s="25">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t>5B. 活动与券变现流水</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="17">
+    <row r="12" ht="15" customHeight="1" s="25">
       <c r="A12" s="1" t="inlineStr">
         <is>
           <t>日期</t>
@@ -4132,105 +4003,105 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1" s="17">
-      <c r="A13" s="10" t="n"/>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
-      <c r="F13" s="10" t="n"/>
-      <c r="G13" s="10" t="n"/>
-      <c r="H13" s="10" t="n"/>
-    </row>
-    <row r="14" ht="16.5" customHeight="1" s="17">
-      <c r="A14" s="10" t="n"/>
-      <c r="B14" s="10" t="n"/>
-      <c r="C14" s="10" t="n"/>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="10" t="n"/>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
-      <c r="H14" s="10" t="n"/>
-    </row>
-    <row r="15" ht="16.5" customHeight="1" s="17">
-      <c r="A15" s="10" t="n"/>
-      <c r="B15" s="10" t="n"/>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="10" t="n"/>
-      <c r="E15" s="10" t="n"/>
-      <c r="F15" s="10" t="n"/>
-      <c r="G15" s="10" t="n"/>
-      <c r="H15" s="10" t="n"/>
-    </row>
-    <row r="16" ht="16.5" customHeight="1" s="17">
-      <c r="A16" s="10" t="n"/>
-      <c r="B16" s="10" t="n"/>
-      <c r="C16" s="10" t="n"/>
-      <c r="D16" s="10" t="n"/>
-      <c r="E16" s="10" t="n"/>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="10" t="n"/>
-      <c r="H16" s="10" t="n"/>
-    </row>
-    <row r="17" ht="16.5" customHeight="1" s="17">
-      <c r="A17" s="10" t="n"/>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
-      <c r="F17" s="10" t="n"/>
-      <c r="G17" s="10" t="n"/>
-      <c r="H17" s="10" t="n"/>
-    </row>
-    <row r="18" ht="16.5" customHeight="1" s="17">
-      <c r="A18" s="10" t="n"/>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="10" t="n"/>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="10" t="n"/>
-      <c r="H18" s="10" t="n"/>
-    </row>
-    <row r="19" ht="16.5" customHeight="1" s="17">
-      <c r="A19" s="10" t="n"/>
-      <c r="B19" s="10" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="10" t="n"/>
-      <c r="F19" s="10" t="n"/>
-      <c r="G19" s="10" t="n"/>
-      <c r="H19" s="10" t="n"/>
-    </row>
-    <row r="20" ht="16.5" customHeight="1" s="17">
-      <c r="A20" s="10" t="n"/>
-      <c r="B20" s="10" t="n"/>
-      <c r="C20" s="10" t="n"/>
-      <c r="D20" s="10" t="n"/>
-      <c r="E20" s="10" t="n"/>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="10" t="n"/>
-      <c r="H20" s="10" t="n"/>
-    </row>
-    <row r="21" ht="16.5" customHeight="1" s="17">
-      <c r="A21" s="10" t="n"/>
-      <c r="B21" s="10" t="n"/>
-      <c r="C21" s="10" t="n"/>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="10" t="n"/>
-      <c r="F21" s="10" t="n"/>
-      <c r="G21" s="10" t="n"/>
-      <c r="H21" s="10" t="n"/>
-    </row>
-    <row r="22" ht="16.5" customHeight="1" s="17">
-      <c r="A22" s="10" t="n"/>
-      <c r="B22" s="10" t="n"/>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="10" t="n"/>
-      <c r="E22" s="10" t="n"/>
-      <c r="F22" s="10" t="n"/>
-      <c r="G22" s="10" t="n"/>
-      <c r="H22" s="10" t="n"/>
+    <row r="13" ht="16.5" customHeight="1" s="25">
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+      <c r="H13" s="8" t="n"/>
+    </row>
+    <row r="14" ht="16.5" customHeight="1" s="25">
+      <c r="A14" s="8" t="n"/>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
+      <c r="H14" s="8" t="n"/>
+    </row>
+    <row r="15" ht="16.5" customHeight="1" s="25">
+      <c r="A15" s="8" t="n"/>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="8" t="n"/>
+      <c r="G15" s="8" t="n"/>
+      <c r="H15" s="8" t="n"/>
+    </row>
+    <row r="16" ht="16.5" customHeight="1" s="25">
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="8" t="n"/>
+    </row>
+    <row r="17" ht="16.5" customHeight="1" s="25">
+      <c r="A17" s="8" t="n"/>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="8" t="n"/>
+      <c r="H17" s="8" t="n"/>
+    </row>
+    <row r="18" ht="16.5" customHeight="1" s="25">
+      <c r="A18" s="8" t="n"/>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="8" t="n"/>
+      <c r="H18" s="8" t="n"/>
+    </row>
+    <row r="19" ht="16.5" customHeight="1" s="25">
+      <c r="A19" s="8" t="n"/>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="8" t="n"/>
+      <c r="H19" s="8" t="n"/>
+    </row>
+    <row r="20" ht="16.5" customHeight="1" s="25">
+      <c r="A20" s="8" t="n"/>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+      <c r="H20" s="8" t="n"/>
+    </row>
+    <row r="21" ht="16.5" customHeight="1" s="25">
+      <c r="A21" s="8" t="n"/>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="8" t="n"/>
+      <c r="G21" s="8" t="n"/>
+      <c r="H21" s="8" t="n"/>
+    </row>
+    <row r="22" ht="16.5" customHeight="1" s="25">
+      <c r="A22" s="8" t="n"/>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="8" t="n"/>
+      <c r="H22" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4249,33 +4120,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
-    <col width="14" customWidth="1" style="17" min="1" max="1"/>
-    <col width="18" customWidth="1" style="17" min="2" max="2"/>
-    <col width="14" customWidth="1" style="17" min="3" max="3"/>
-    <col width="12" customWidth="1" style="17" min="4" max="4"/>
-    <col width="14" customWidth="1" style="17" min="5" max="5"/>
-    <col width="18" customWidth="1" style="17" min="6" max="6"/>
+    <col width="14" customWidth="1" style="25" min="1" max="1"/>
+    <col width="18" customWidth="1" style="25" min="2" max="2"/>
+    <col width="14" customWidth="1" style="25" min="3" max="3"/>
+    <col width="12" customWidth="1" style="25" min="4" max="4"/>
+    <col width="14" customWidth="1" style="25" min="5" max="5"/>
+    <col width="18" customWidth="1" style="25" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" s="17">
-      <c r="A1" s="18" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="25">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>收支总账 — 年度盈亏（年费支出 vs 变现收入）</t>
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3" ht="15" customHeight="1" s="17">
-      <c r="A3" s="19" t="inlineStr">
+    <row r="3" ht="15" customHeight="1" s="25">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>6A. 支出（年费）</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="17">
+    <row r="4" ht="15" customHeight="1" s="25">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>银行</t>
@@ -4307,305 +4177,370 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="16.5" customHeight="1" s="17">
-      <c r="A5" s="10" t="inlineStr">
+    <row r="5" ht="16.5" customHeight="1" s="25">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>中信</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>南航卡</t>
         </is>
       </c>
-      <c r="C5" s="10" t="n">
+      <c r="C5" s="8" t="n">
         <v>480</v>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>刚性</t>
         </is>
       </c>
-      <c r="E5" s="10" t="n">
+      <c r="E5" s="8" t="n">
         <v>480</v>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>4月24日</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="16.5" customHeight="1" s="17">
-      <c r="A6" s="10" t="inlineStr">
+    <row r="6" ht="16.5" customHeight="1" s="25">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>交通</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>东航卡</t>
         </is>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>刚性</t>
         </is>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>12月30日</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1" s="17">
-      <c r="A7" s="10" t="inlineStr">
+    <row r="7" ht="16.5" customHeight="1" s="25">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>兴业</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>行悠白</t>
         </is>
       </c>
-      <c r="C7" s="10" t="n">
+      <c r="C7" s="8" t="n">
         <v>900</v>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>刚性</t>
         </is>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E7" s="8" t="n">
         <v>900</v>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>8月26日</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="16.5" customHeight="1" s="17">
-      <c r="A8" s="29" t="inlineStr">
+    <row r="8" ht="16.5" customHeight="1" s="25">
+      <c r="A8" s="37" t="inlineStr">
+        <is>
+          <t>光大</t>
+        </is>
+      </c>
+      <c r="B8" s="37" t="inlineStr">
+        <is>
+          <t>阳光车主</t>
+        </is>
+      </c>
+      <c r="C8" s="37" t="n">
+        <v>500</v>
+      </c>
+      <c r="D8" s="37" t="inlineStr">
+        <is>
+          <t>积分抵扣</t>
+        </is>
+      </c>
+      <c r="E8" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="37" t="inlineStr">
+        <is>
+          <t>10W积分</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="37" t="inlineStr">
+        <is>
+          <t>宁波</t>
+        </is>
+      </c>
+      <c r="B9" s="37" t="inlineStr">
+        <is>
+          <t>菁英卡</t>
+        </is>
+      </c>
+      <c r="C9" s="37" t="n">
+        <v>1800</v>
+      </c>
+      <c r="D9" s="37" t="inlineStr">
+        <is>
+          <t>消费额度</t>
+        </is>
+      </c>
+      <c r="E9" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="37" t="inlineStr">
+        <is>
+          <t>18W</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="25">
+      <c r="A10" s="41" t="inlineStr"/>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="25">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B8" s="15" t="n"/>
-      <c r="C8" s="13">
-        <f>SUM(C5:C7)</f>
+      <c r="B11" s="39" t="n"/>
+      <c r="C11" s="38">
+        <f>SUM(C5:C9)</f>
         <v/>
       </c>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13">
-        <f>SUM(E5:E7)</f>
+      <c r="D11" s="40" t="n"/>
+      <c r="E11" s="38">
+        <f>SUM(E5:E9)</f>
         <v/>
       </c>
-      <c r="F8" s="13" t="n"/>
-    </row>
-    <row r="9"/>
-    <row r="10" ht="15" customHeight="1" s="17">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="F11" s="40" t="n"/>
+    </row>
+    <row r="12" ht="16.5" customHeight="1" s="25"/>
+    <row r="13" ht="16.5" customHeight="1" s="25">
+      <c r="A13" s="32" t="inlineStr">
         <is>
           <t>6B. 收入（权益变现 + 券变现）</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="17">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="14" ht="16.5" customHeight="1" s="25">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>预估年收入</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>26年已实现</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16.5" customHeight="1" s="17">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16.5" customHeight="1" s="25">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>权益变现</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>2,850-4,988</t>
         </is>
       </c>
-      <c r="C12" s="10" t="n">
+      <c r="C15" s="8" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1" s="17">
-      <c r="A13" s="10" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>券变现</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="n">
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1" s="17">
-      <c r="A14" s="10" t="inlineStr">
+    <row r="17" ht="15" customHeight="1" s="25">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>活动返现</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="n">
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1" s="17">
-      <c r="A15" s="13" t="inlineStr">
+    <row r="18" ht="15" customHeight="1" s="25">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>2,850-4,988</t>
         </is>
       </c>
-      <c r="C15" s="13" t="n">
+      <c r="C18" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n"/>
-    </row>
-    <row r="16"/>
-    <row r="17" ht="15" customHeight="1" s="17">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+    </row>
+    <row r="19" ht="16.5" customHeight="1" s="25"/>
+    <row r="20" ht="16.5" customHeight="1" s="25">
+      <c r="A20" s="32" t="inlineStr">
         <is>
           <t>6C. 盈亏汇总</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="17">
-      <c r="A18" s="1" t="inlineStr">
+    <row r="21" ht="16.5" customHeight="1" s="25">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>项目</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr">
+      <c r="B21" s="1" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E18" s="1" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F18" s="1" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="16.5" customHeight="1" s="17">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>总支出（年费）</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>4,180 元</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="16.5" customHeight="1" s="17">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="42" t="inlineStr">
+        <is>
+          <t>预估净盈亏</t>
+        </is>
+      </c>
+      <c r="B22" s="43" t="inlineStr">
+        <is>
+          <t>+1,270 ~ +3,588 元</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="25">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>预估收入</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>2,850-4,988 元</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="16.5" customHeight="1" s="17">
-      <c r="A21" s="10" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>预估净盈亏</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>-1,330 ~ +808 元</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23" ht="15.75" customHeight="1" s="17">
-      <c r="A23" s="16" t="inlineStr">
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="24" t="inlineStr">
         <is>
           <t>目标：收入覆盖刚性年费（中信480+交通500+兴业900=1,880），剩余积分/消费类年费靠刷卡自然达标。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A11:B11"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A8:B8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="1200" verticalDpi="1200"/>
 </worksheet>
 </file>
 
@@ -4619,28 +4554,28 @@
   <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
-    <col width="10" customWidth="1" style="17" min="1" max="1"/>
-    <col width="12" customWidth="1" style="17" min="2" max="2"/>
-    <col width="10" customWidth="1" style="17" min="3" max="5"/>
-    <col width="8" customWidth="1" style="17" min="6" max="6"/>
-    <col width="10" customWidth="1" style="17" min="7" max="8"/>
+    <col width="10" customWidth="1" style="25" min="1" max="1"/>
+    <col width="12" customWidth="1" style="25" min="2" max="2"/>
+    <col width="10" customWidth="1" style="25" min="3" max="5"/>
+    <col width="8" customWidth="1" style="25" min="6" max="6"/>
+    <col width="10" customWidth="1" style="25" min="7" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" s="17">
-      <c r="A1" s="18" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="25">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>积分余额 — 各卡积分追踪</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="17">
-      <c r="A2" s="16" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="25">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>待补充：当前积分余额数据，后续提供具体值 → 填入「当前余额」列</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="17">
+    <row r="3" ht="15" customHeight="1" s="25">
       <c r="A3" s="1" t="inlineStr">
         <is>
           <t>银行</t>
@@ -4682,287 +4617,287 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1" s="17">
-      <c r="A4" s="10" t="inlineStr">
+    <row r="4" ht="16.5" customHeight="1" s="25">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>建行</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>大山白</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>综合积分</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="n">
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="n">
         <v>400000</v>
       </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>年费</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16.5" customHeight="1" s="17">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16.5" customHeight="1" s="25">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>邮储</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>鼎致白</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>综合积分</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="n">
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="n">
         <v>200000</v>
       </c>
-      <c r="F5" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>年费</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16.5" customHeight="1" s="17">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16.5" customHeight="1" s="25">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>光大</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>阳光车主</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>综合积分</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="n">
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="n">
         <v>100000</v>
       </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>年费</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16.5" customHeight="1" s="17">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16.5" customHeight="1" s="25">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>民生</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>百夫长</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>综合积分</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="n">
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="n">
         <v>200000</v>
       </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>年费</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16.5" customHeight="1" s="17">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16.5" customHeight="1" s="25">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>农行</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>精粹白</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>综合积分</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>里程</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16.5" customHeight="1" s="17">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16.5" customHeight="1" s="25">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>广发</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>尊旅卡</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>综合积分</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>里程</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16.5" customHeight="1" s="17">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" s="25">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>京彩卡</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>综合积分</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>国航里程</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4992,400 +4927,400 @@
   <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
-    <col width="14" customWidth="1" style="17" min="1" max="1"/>
-    <col width="10" customWidth="1" style="17" min="2" max="2"/>
-    <col width="12" customWidth="1" style="17" min="3" max="3"/>
-    <col width="40" customWidth="1" style="17" min="4" max="4"/>
-    <col width="10" customWidth="1" style="17" min="5" max="5"/>
-    <col width="20" customWidth="1" style="17" min="6" max="6"/>
+    <col width="14" customWidth="1" style="25" min="1" max="1"/>
+    <col width="10" customWidth="1" style="25" min="2" max="2"/>
+    <col width="12" customWidth="1" style="25" min="3" max="3"/>
+    <col width="40" customWidth="1" style="25" min="4" max="4"/>
+    <col width="10" customWidth="1" style="25" min="5" max="5"/>
+    <col width="20" customWidth="1" style="25" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" s="17">
-      <c r="A1" s="20" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="25">
+      <c r="A1" s="33" t="inlineStr">
         <is>
           <t>日常记录 — 申请二卡、提额、销卡等操作记录</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="24.95" customHeight="1" s="17">
-      <c r="A2" s="11" t="inlineStr">
+    <row r="2" ht="24.95" customHeight="1" s="25">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>银行</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>操作类型</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>操作详情</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t>结果</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="21.95" customHeight="1" s="17">
-      <c r="A3" s="12" t="inlineStr">
+    <row r="3" ht="21.95" customHeight="1" s="25">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>工商</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>申请提额</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>申请提额至10W</t>
         </is>
       </c>
-      <c r="E3" s="40" t="inlineStr">
+      <c r="E3" s="21" t="inlineStr">
         <is>
           <t>✅成功</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>10W额度获批</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="21.95" customHeight="1" s="17">
-      <c r="A4" s="12" t="inlineStr">
+    <row r="4" ht="21.95" customHeight="1" s="25">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>广发</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>申请提额</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>自动出现额度，直接申请</t>
         </is>
       </c>
-      <c r="E4" s="40" t="inlineStr">
+      <c r="E4" s="21" t="inlineStr">
         <is>
           <t>✅成功</t>
         </is>
       </c>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>申请的是VISA卡！</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="21.95" customHeight="1" s="17">
-      <c r="A5" s="12" t="inlineStr">
+    <row r="5" ht="21.95" customHeight="1" s="25">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>建行</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>申请提额</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>申请提额</t>
         </is>
       </c>
-      <c r="E5" s="41" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>❌拒绝</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="21.95" customHeight="1" s="17">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="21.95" customHeight="1" s="25">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>招商</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>办理二卡</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E6" s="42" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
         <is>
           <t>待记录</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="21.95" customHeight="1" s="17">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="21.95" customHeight="1" s="25">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>中信</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>办理二卡</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="42" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>待记录</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="21.95" customHeight="1" s="17">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="21.95" customHeight="1" s="25">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>中信</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>提额</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>APP人工提额度，授权了个税记录</t>
         </is>
       </c>
-      <c r="E8" s="42" t="inlineStr">
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t>待结果</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="21.95" customHeight="1" s="17">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="21.95" customHeight="1" s="25">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>农行</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>申请提额</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>申请12W</t>
         </is>
       </c>
-      <c r="E9" s="41" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>❌未通过</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="21.95" customHeight="1" s="17">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="21.95" customHeight="1" s="25">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>农行</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>申请提额</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>再次申请15W</t>
         </is>
       </c>
-      <c r="E10" s="41" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>❌未通过</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="21.95" customHeight="1" s="17">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="21.95" customHeight="1" s="25">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>农行</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>申请提额</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>申请10W</t>
         </is>
       </c>
-      <c r="E11" s="41" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>❌未通过</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="21.95" customHeight="1" s="17">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="21.95" customHeight="1" s="25">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>光大</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>申请提额</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>没有申请按钮，需要分期？</t>
         </is>
       </c>
-      <c r="E12" s="42" t="inlineStr">
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="21.95" customHeight="1" s="17">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="21.95" customHeight="1" s="25">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>邮储</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>申请提额</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>没有申请按钮，需要分期？</t>
         </is>
       </c>
-      <c r="E13" s="42" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/02-Knowledge/investment-research/credit-card-management/信用卡主控表.xlsx
+++ b/02-Knowledge/investment-research/credit-card-management/信用卡主控表.xlsx
@@ -219,7 +219,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -322,11 +322,39 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -435,6 +463,11 @@
     <xf numFmtId="0" fontId="15" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3571,35 +3604,21 @@
       </c>
     </row>
     <row r="16" ht="16.5" customHeight="1" s="25">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="44" t="inlineStr">
         <is>
           <t>宁波</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>贵宾厅</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="D16" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="B16" s="28" t="n"/>
+      <c r="C16" s="28" t="n"/>
+      <c r="D16" s="28" t="n"/>
+      <c r="E16" s="29" t="n"/>
+      <c r="F16" s="44" t="inlineStr">
         <is>
           <t>50-80</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>600-960</t>
-        </is>
-      </c>
+      <c r="G16" s="29" t="n"/>
       <c r="H16" s="8" t="inlineStr">
         <is>
           <t>实名</t>
@@ -3612,16 +3631,25 @@
           <t>合计</t>
         </is>
       </c>
-      <c r="B17" s="39" t="n"/>
-      <c r="C17" s="39" t="n"/>
-      <c r="D17" s="39" t="n"/>
-      <c r="E17" s="39" t="n"/>
+      <c r="B17" s="45" t="n"/>
+      <c r="C17">
+        <f>SUM(C5:C15)</f>
+        <v/>
+      </c>
+      <c r="D17">
+        <f>SUM(D5:D15)</f>
+        <v/>
+      </c>
+      <c r="E17">
+        <f>SUM(E5:E15)</f>
+        <v/>
+      </c>
       <c r="F17" s="38" t="inlineStr">
         <is>
           <t>3,150-5,468 元</t>
         </is>
       </c>
-      <c r="G17" s="39" t="n"/>
+      <c r="G17" s="45" t="n"/>
       <c r="H17" s="40" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1" s="25"/>
@@ -3776,8 +3804,8 @@
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="F16:G16"/>
+    <mergeCell ref="A17:B17"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A17:E17"/>
     <mergeCell ref="F17:G17"/>
   </mergeCells>
   <conditionalFormatting sqref="E5:E15">
@@ -4267,11 +4295,7 @@
           <t>光大</t>
         </is>
       </c>
-      <c r="B8" s="37" t="inlineStr">
-        <is>
-          <t>阳光车主</t>
-        </is>
-      </c>
+      <c r="B8" s="45" t="n"/>
       <c r="C8" s="37" t="n">
         <v>500</v>
       </c>
@@ -4323,6 +4347,11 @@
     </row>
     <row r="10" ht="15" customHeight="1" s="25">
       <c r="A10" s="41" t="inlineStr"/>
+      <c r="B10" s="46" t="n"/>
+      <c r="C10" s="46" t="n"/>
+      <c r="D10" s="46" t="n"/>
+      <c r="E10" s="46" t="n"/>
+      <c r="F10" s="45" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1" s="25">
       <c r="A11" s="38" t="inlineStr">
@@ -4330,7 +4359,7 @@
           <t>合计</t>
         </is>
       </c>
-      <c r="B11" s="39" t="n"/>
+      <c r="B11" s="45" t="n"/>
       <c r="C11" s="38">
         <f>SUM(C5:C9)</f>
         <v/>
@@ -4413,19 +4442,16 @@
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="25">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="44" t="inlineStr">
         <is>
           <t>活动返现</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="n">
-        <v>0</v>
-      </c>
+      <c r="B17" s="28" t="n"/>
+      <c r="C17" s="28" t="n"/>
+      <c r="D17" s="28" t="n"/>
+      <c r="E17" s="28" t="n"/>
+      <c r="F17" s="29" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1" s="25">
       <c r="A18" s="11" t="inlineStr">
@@ -4498,16 +4524,16 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="25">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="44" t="inlineStr">
         <is>
           <t>预估收入</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>2,850-4,988 元</t>
-        </is>
-      </c>
+      <c r="B23" s="28" t="n"/>
+      <c r="C23" s="28" t="n"/>
+      <c r="D23" s="28" t="n"/>
+      <c r="E23" s="28" t="n"/>
+      <c r="F23" s="29" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -4521,7 +4547,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
         <is>
@@ -4533,8 +4558,8 @@
   <mergeCells count="7">
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A11:B11"/>
     <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A11:B11"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A8:B8"/>
